--- a/config/excel/CfgGuide.xlsx
+++ b/config/excel/CfgGuide.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="R186b36e7fb484ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="R7b52a58ff7a34498"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -29,8 +29,23 @@
       <x:color rgb="FF172B35"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -40,6 +55,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1E4054"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -49,11 +79,23 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -256,135 +298,149 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="100" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="27" customHeight="1">
-      <x:c r="A1" s="2" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>SortOrder</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>Title</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>Body</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
-      <x:c r="A2" s="3" t="str">
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="7" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="7" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
-      <x:c r="A3" s="3" t="str">
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="9" t="str">
+        <x:v># movement</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>移动与战斗</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>拖动摇杆移动角色。敌人进入角色的近战范围后，角色会自动使用基础攻击。留意生命值和敌人的地面预警。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="76" customHeight="1">
+      <x:c r="A4" s="11" t="str">
         <x:v>movement</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="n">
+      <x:c r="B4" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="C4" s="11" t="str">
         <x:v>移动与战斗</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D4" s="11" t="str">
         <x:v>拖动摇杆移动角色。敌人进入角色的近战范围后，角色会自动使用基础攻击。留意生命值和敌人的地面预警。</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
-      <x:c r="A4" s="3" t="str">
+    <x:row r="5" ht="76" customHeight="1">
+      <x:c r="A5" s="11" t="str">
         <x:v>exploration</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="n">
+      <x:c r="B5" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
-        <x:v>探索地图</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="str">
-        <x:v>房间尚未清空时也可以走向相连房间，自由往返。小地图显示探索位置，但不标出撤离点；请在场景中寻找撤离入口。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="27" customHeight="1">
-      <x:c r="A5" s="3" t="str">
+      <x:c r="C5" s="11" t="str">
+        <x:v>探索区域</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>每个区域是一张完整地图，可以自由探索。小地图显示附近精英、宝箱、商人、尾王和出口；打开区域大地图可拖动、缩放并追踪目标。尾王领奖完成后，出口允许带回结束或单向进入下一区域。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="76" customHeight="1">
+      <x:c r="A6" s="11" t="str">
         <x:v>loot</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="n">
+      <x:c r="B6" s="11" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="str">
-        <x:v>拾取与装备</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="str">
-        <x:v>靠近战利品并拾取，打开局内背包查看物品。武器和护甲可以在局内穿脱，换装前可预览属性。安全箱当前有 {SafeSlots} 格，放入其中的物品受死亡保护。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="27" customHeight="1">
-      <x:c r="A6" s="3" t="str">
+      <x:c r="C6" s="11" t="str">
+        <x:v>物品与收藏</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>宝箱和商人库存会在进入区域时固定。武器、护甲可在背包中穿脱，安全箱有 {SafeSlots} 格。收藏能否入箱以物品资格为准；实际带回仓库后登记图鉴，重复可出售，收藏成就持续提供属性。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="76" customHeight="1">
+      <x:c r="A7" s="11" t="str">
         <x:v>outcome</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="n">
+      <x:c r="B7" s="11" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="str">
-        <x:v>撤离与死亡</x:v>
-      </x:c>
-      <x:c r="D6" s="3" t="str">
-        <x:v>成功撤离可带出本局取得的全部物品。死亡会失去安全箱外的入场装备和战利品。主动放弃按死亡结算，入场消耗的体力不会退还。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="27" customHeight="1">
-      <x:c r="A7" s="3" t="str">
+      <x:c r="C7" s="11" t="str">
+        <x:v>结束与续局</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>完成区域尾王的全部奖励后，可在出口带回全部持有物或继续深入。最终Boss全部领奖后自动通关。死亡或主动放弃只保留安全箱物品，不退体力。应用意外中断后可在主界面继续原关卡。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="76" customHeight="1">
+      <x:c r="A8" s="11" t="str">
         <x:v>rogue</x:v>
       </x:c>
-      <x:c r="B7" s="3" t="n">
+      <x:c r="B8" s="11" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="str">
-        <x:v>局内三选一</x:v>
-      </x:c>
-      <x:c r="D7" s="3" t="str">
-        <x:v>清理房间后可能出现三选一奖励。选择时战斗暂停；可获得临时强化、随机战利品或流派升级。局内强化不会写入局外技能等级。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="27" customHeight="1">
-      <x:c r="A8" s="3" t="str">
+      <x:c r="C8" s="11" t="str">
+        <x:v>技能与尾王奖励</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>击杀普通怪和精英积累技能进度，到达门槛后暂停并选择一项局内技能；已满级技能不再出现，技能全部选完后不再发技能选择。尾王另行提供装备和收藏候选，多轮奖励须逐轮领取。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="76" customHeight="1">
+      <x:c r="A9" s="11" t="str">
         <x:v>progression</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="n">
+      <x:c r="B9" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="str">
-        <x:v>局外成长</x:v>
-      </x:c>
-      <x:c r="D8" s="3" t="str">
-        <x:v>打怪和成功撤离可获得经验，升级后获得技能点。在主界面的技能入口提升局外技能；已保存的技能等级和剩余点数不会随死亡丢失。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="27" customHeight="1">
-      <x:c r="A9" s="3" t="str">
+      <x:c r="C9" s="11" t="str">
+        <x:v>长期成长</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>打怪和成功结束获得经验，升级后获得技能点；主界面技能用于局外提升。收藏实际入库后登记成就，奖励属性只生效一次。死亡不清除已经保存的等级、局外技能与收藏成就。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="76" customHeight="1">
+      <x:c r="A10" s="11" t="str">
         <x:v>stamina</x:v>
       </x:c>
-      <x:c r="B9" s="3" t="n">
+      <x:c r="B10" s="11" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="str">
+      <x:c r="C10" s="11" t="str">
         <x:v>体力与补给</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="str">
+      <x:c r="D10" s="11" t="str">
         <x:v>每局入场消耗 {EntryCost} 点体力，上限 {StaminaCap} 点；每 {RecoverySeconds} 秒恢复 1 点，每天 {DailyResetHour} 点重置到上限。每天 {SupplyHourFirst} 点、{SupplyHourSecond} 点、{SupplyHourThird} 点可手动领取 {SupplyAmount} 点补给。</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgGuide.xlsx
+++ b/config/excel/CfgGuide.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="R7b52a58ff7a34498"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="R7f18a9fbeb21497a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -385,7 +385,7 @@
         <x:v>物品与收藏</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>宝箱和商人库存会在进入区域时固定。武器、护甲可在背包中穿脱，安全箱有 {SafeSlots} 格。收藏能否入箱以物品资格为准；实际带回仓库后登记图鉴，重复可出售，收藏成就持续提供属性。</x:v>
+        <x:v>宝箱和商人库存会在进入区域时固定。武器、护甲可在背包中穿脱。收藏在成功结束带回仓库后登记图鉴，重复可出售，收藏成就持续提供属性。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="76" customHeight="1">
@@ -399,7 +399,7 @@
         <x:v>结束与续局</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>完成区域尾王的全部奖励后，可在出口带回全部持有物或继续深入。最终Boss全部领奖后自动通关。死亡或主动放弃只保留安全箱物品，不退体力。应用意外中断后可在主界面继续原关卡。</x:v>
+        <x:v>完成区域尾王的全部奖励后，可在出口带回全部持有物或继续深入。最终Boss全部领奖后自动通关。死亡时可看广告原地满血复活，全部持有物保留且不限次数；确认死亡结算或主动放弃会损失全部持有物，不退体力。应用意外中断后可在主界面继续原关卡。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="76" customHeight="1">

--- a/config/excel/CfgGuide.xlsx
+++ b/config/excel/CfgGuide.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="R7f18a9fbeb21497a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="Rc72638a6cf8e4473"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -22,30 +22,10 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF172B35"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Microsoft YaHei"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -54,48 +34,26 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1E4054"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FF17365D"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFDBEAF7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -297,151 +255,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="100" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="2" t="str">
         <x:v>SortOrder</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="2" t="str">
         <x:v>Title</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="2" t="str">
         <x:v>Body</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="7" t="str">
+    <x:row r="2">
+      <x:c r="A2" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="B2" s="7" t="str">
+      <x:c r="B2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="7" t="str">
+      <x:c r="C2" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="str">
+      <x:c r="D2" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="9" t="str">
-        <x:v># movement</x:v>
-      </x:c>
-      <x:c r="B3" s="9" t="n">
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>movement</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="str">
+      <x:c r="C3" t="str">
         <x:v>移动与战斗</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="str">
-        <x:v>拖动摇杆移动角色。敌人进入角色的近战范围后，角色会自动使用基础攻击。留意生命值和敌人的地面预警。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="76" customHeight="1">
-      <x:c r="A4" s="11" t="str">
-        <x:v>movement</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="str">
-        <x:v>移动与战斗</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="str">
-        <x:v>拖动摇杆移动角色。敌人进入角色的近战范围后，角色会自动使用基础攻击。留意生命值和敌人的地面预警。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="76" customHeight="1">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="D3" t="str">
+        <x:v>拖动摇杆移动角色，敌人进入近战范围后自动攻击。留意生命值和地面预警，完成当前房间目标后向上方出口前进。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
         <x:v>exploration</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="n">
+      <x:c r="B4" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="str">
-        <x:v>探索区域</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>每个区域是一张完整地图，可以自由探索。小地图显示附近精英、宝箱、商人、尾王和出口；打开区域大地图可拖动、缩放并追踪目标。尾王领奖完成后，出口允许带回结束或单向进入下一区域。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="76" customHeight="1">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="C4" t="str">
+        <x:v>线性房间关卡</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>房间按顺序单向推进，最后为Boss房；怪物房清场后开放出口，最终Boss奖励领取完毕后通关并带回收益。当前六房排列是可调原型，包含怪物房、宝箱房和商人房。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
         <x:v>loot</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="B5" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>物品与收藏</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>宝箱和商人库存会在进入区域时固定。武器、护甲可在背包中穿脱。收藏在成功结束带回仓库后登记图鉴，重复可出售，收藏成就持续提供属性。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="76" customHeight="1">
-      <x:c r="A7" s="11" t="str">
+      <x:c r="C5" t="str">
+        <x:v>出战装备与关卡背包</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>进入关卡后装备固定，携入装备受保护。关卡背包与主城仓库独立，本关获得物品在通关或广告携物撤离后才能带出。中途死亡退出或放弃只损失本关所得，携入装备保留。收藏实际带回入库后登记，成就属性只奖励一次。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
         <x:v>outcome</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="n">
+      <x:c r="B6" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="str">
-        <x:v>结束与续局</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>完成区域尾王的全部奖励后，可在出口带回全部持有物或继续深入。最终Boss全部领奖后自动通关。死亡时可看广告原地满血复活，全部持有物保留且不限次数；确认死亡结算或主动放弃会损失全部持有物，不退体力。应用意外中断后可在主界面继续原关卡。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="76" customHeight="1">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="C6" t="str">
+        <x:v>复活与携物撤离</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>死亡后可以观看广告复活并继续当前战斗。也可以观看广告，从关卡背包选择最多{AdExtractionItemLimit}件物品撤离，选中物品带回，其余本关所得损失；携物撤离结束当前关卡，不能重复提取，也不视为通关。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
         <x:v>rogue</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="n">
+      <x:c r="B7" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>技能与尾王奖励</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>击杀普通怪和精英积累技能进度，到达门槛后暂停并选择一项局内技能；已满级技能不再出现，技能全部选完后不再发技能选择。尾王另行提供装备和收藏候选，多轮奖励须逐轮领取。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="76" customHeight="1">
-      <x:c r="A9" s="11" t="str">
+      <x:c r="C7" t="str">
+        <x:v>永久经验与技能点</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>击杀怪物获得永久经验，升级提升角色属性并获得技能点，技能点用于升级技能。等级、经验和已经获得的技能点不因死亡退出而清除；重开房间时已确认领奖的敌人槽位不重复发放经验或掉落。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
         <x:v>progression</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="n">
+      <x:c r="B8" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>长期成长</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>打怪和成功结束获得经验，升级后获得技能点；主界面技能用于局外提升。收藏实际入库后登记成就，奖励属性只生效一次。死亡不清除已经保存的等级、局外技能与收藏成就。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="76" customHeight="1">
-      <x:c r="A10" s="11" t="str">
+      <x:c r="C8" t="str">
+        <x:v>暂离与继续</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>暂离主城保留关卡背包、角色收益和消耗。未完成的怪物或Boss战再次进入时重开，已确认的敌人收益不重复发放。未领取完的宝箱房保留；离开NPC房后继续下一房。已击败Boss但尚未领奖时继续处理原奖励。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
         <x:v>stamina</x:v>
       </x:c>
-      <x:c r="B10" s="11" t="n">
+      <x:c r="B9" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>体力与补给</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>每局入场消耗 {EntryCost} 点体力，上限 {StaminaCap} 点；每 {RecoverySeconds} 秒恢复 1 点，每天 {DailyResetHour} 点重置到上限。每天 {SupplyHourFirst} 点、{SupplyHourSecond} 点、{SupplyHourThird} 点可手动领取 {SupplyAmount} 点补给。</x:v>
+      <x:c r="C9" t="str">
+        <x:v>入场体力与补给</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>首次开启关卡消耗{EntryCost}点体力，每次进入房间消耗{RoomEntryCost}点；继续宝箱房不额外扣费，重新进入未完成怪物或Boss房仍消耗{RoomEntryCost}点。体力上限{StaminaCap}点，每{RecoverySeconds}秒恢复1点，每天{DailyResetHour}点重置到上限。每天{SupplyHourFirst}点、{SupplyHourSecond}点、{SupplyHourThird}点可手动领取{SupplyAmount}点补给。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgGuide.xlsx
+++ b/config/excel/CfgGuide.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="Rc72638a6cf8e4473"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="R030fbb219f39463b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,29 +13,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="1">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="2">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF17365D"/>
-      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -50,10 +39,8 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -257,16 +244,16 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="2" t="str">
+      <x:c r="A1" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="str">
+      <x:c r="B1" t="str">
         <x:v>SortOrder</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="str">
+      <x:c r="C1" t="str">
         <x:v>Title</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="str">
+      <x:c r="D1" t="str">
         <x:v>Body</x:v>
       </x:c>
     </x:row>
@@ -295,7 +282,7 @@
         <x:v>移动与战斗</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>拖动摇杆移动角色，敌人进入近战范围后自动攻击。留意生命值和地面预警，完成当前房间目标后向上方出口前进。</x:v>
+        <x:v>拖动摇杆移动角色，敌人进入近战范围后自动攻击。触碰NPC、未领取宝箱或已开放出口时自动打开对应窗口并暂停战斗，无需按键或点击主界面互动按钮。留意生命值和地面预警，完成当前房间目标后向上方出口前进。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -309,7 +296,7 @@
         <x:v>线性房间关卡</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>房间按顺序单向推进，最后为Boss房；怪物房清场后开放出口，最终Boss奖励领取完毕后通关并带回收益。当前六房排列是可调原型，包含怪物房、宝箱房和商人房。</x:v>
+        <x:v>房间按顺序单向推进，最后为Boss房；怪物房清场后开放出口，最终Boss奖励领取完毕后自动通关并带回收益。关闭NPC或出口窗口后，先离开触碰范围，再进入即可重新打开；站在原地不会反复弹窗，宝箱领取后不再触发。当前六房排列是可调原型，包含怪物房、宝箱房和商人房。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -379,7 +366,7 @@
         <x:v>入场体力与补给</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>首次开启关卡消耗{EntryCost}点体力，每次进入房间消耗{RoomEntryCost}点；继续宝箱房不额外扣费，重新进入未完成怪物或Boss房仍消耗{RoomEntryCost}点。体力上限{StaminaCap}点，每{RecoverySeconds}秒恢复1点，每天{DailyResetHour}点重置到上限。每天{SupplyHourFirst}点、{SupplyHourSecond}点、{SupplyHourThird}点可手动领取{SupplyAmount}点补给。</x:v>
+        <x:v>首次开启关卡只消耗{EntryCost}点体力，第一房不另收费；后续每进入一个新房间消耗{RoomEntryCost}点。继续宝箱房不扣费，继续未完成怪物或Boss房消耗{RoomEntryCost}点；NPC房续关直接进入下一房并消耗{RoomEntryCost}点。最终Boss已全部领奖、仅待补办通关时恢复免费。体力上限{StaminaCap}点，每{RecoverySeconds}秒恢复1点，每天{DailyResetHour}点重置到上限。每天{SupplyHourFirst}点、{SupplyHourSecond}点、{SupplyHourThird}点可手动领取{SupplyAmount}点补给。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgGuide.xlsx
+++ b/config/excel/CfgGuide.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="R030fbb219f39463b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="Rd4616a990aaa4dc6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -296,7 +296,7 @@
         <x:v>线性房间关卡</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>房间按顺序单向推进，最后为Boss房；怪物房清场后开放出口，最终Boss奖励领取完毕后自动通关并带回收益。关闭NPC或出口窗口后，先离开触碰范围，再进入即可重新打开；站在原地不会反复弹窗，宝箱领取后不再触发。当前六房排列是可调原型，包含怪物房、宝箱房和商人房。</x:v>
+        <x:v>房间按顺序单向推进，最后为Boss房；怪物房清场后开放出口。最终Boss击败后出现奖励宝箱，触碰开启后按原有轮次选择战利品，全部领取后开放上方出口；触碰最终出口打开结算对话框，确认后通关并带回收益。关闭NPC或出口窗口后，先离开触碰范围，再进入即可重新打开；站在原地不会反复弹窗，已领取完的宝箱不再触发。当前六房排列是可调原型，包含怪物房、宝箱房和商人房。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -352,7 +352,7 @@
         <x:v>暂离与继续</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>暂离主城保留关卡背包、角色收益和消耗。未完成的怪物或Boss战再次进入时重开，已确认的敌人收益不重复发放。未领取完的宝箱房保留；离开NPC房后继续下一房。已击败Boss但尚未领奖时继续处理原奖励。</x:v>
+        <x:v>暂离主城保留关卡背包、角色收益和消耗。未完成的怪物或Boss战再次进入时重开，已确认的敌人收益不重复发放。未领取完的宝箱房保留；离开NPC房后继续下一房。最终Boss已击败但宝箱未开或奖励未领完时，继续回到本房领取，敌人不重生，冻结候选与已领取事实保留；全部领奖后仍需走到出口确认结算。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -366,7 +366,7 @@
         <x:v>入场体力与补给</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>首次开启关卡只消耗{EntryCost}点体力，第一房不另收费；后续每进入一个新房间消耗{RoomEntryCost}点。继续宝箱房不扣费，继续未完成怪物或Boss房消耗{RoomEntryCost}点；NPC房续关直接进入下一房并消耗{RoomEntryCost}点。最终Boss已全部领奖、仅待补办通关时恢复免费。体力上限{StaminaCap}点，每{RecoverySeconds}秒恢复1点，每天{DailyResetHour}点重置到上限。每天{SupplyHourFirst}点、{SupplyHourSecond}点、{SupplyHourThird}点可手动领取{SupplyAmount}点补给。</x:v>
+        <x:v>首次开启关卡只消耗{EntryCost}点体力，第一房不另收费；后续每进入一个新房间消耗{RoomEntryCost}点。继续宝箱房不扣费，继续未完成怪物或Boss战消耗{RoomEntryCost}点；NPC房续关直接进入下一房并消耗{RoomEntryCost}点。最终Boss已击败后的宝箱领取及出口结算阶段继续免费，死亡待选仍须按原选择处理。体力上限{StaminaCap}点，每{RecoverySeconds}秒恢复1点，每天{DailyResetHour}点重置到上限。每天{SupplyHourFirst}点、{SupplyHourSecond}点、{SupplyHourThird}点可手动领取{SupplyAmount}点补给。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgGuide.xlsx
+++ b/config/excel/CfgGuide.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="Rd4616a990aaa4dc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgGuide" sheetId="1" r:id="R4272c080b5194b7d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -296,7 +296,7 @@
         <x:v>线性房间关卡</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>房间按顺序单向推进，最后为Boss房；怪物房清场后开放出口。最终Boss击败后出现奖励宝箱，触碰开启后按原有轮次选择战利品，全部领取后开放上方出口；触碰最终出口打开结算对话框，确认后通关并带回收益。关闭NPC或出口窗口后，先离开触碰范围，再进入即可重新打开；站在原地不会反复弹窗，已领取完的宝箱不再触发。当前六房排列是可调原型，包含怪物房、宝箱房和商人房。</x:v>
+        <x:v>房间按顺序单向推进，最后为Boss房；怪物房清场后开放出口。最终Boss击败后出现奖励宝箱，触碰开启后展示本箱已经冻结的全部物品，只需点击一次领取按钮即可全部获得，不逐件选择、不分轮。领取完成后开放上方出口；触碰最终出口打开结算对话框，确认后通关并带回收益。关闭NPC、未领宝箱或出口窗口后，先离开触碰范围再进入可重新打开，站在原地不反复弹窗，已领取宝箱不再触发。当前六房排列是可调原型。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -352,7 +352,7 @@
         <x:v>暂离与继续</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>暂离主城保留关卡背包、角色收益和消耗。未完成的怪物或Boss战再次进入时重开，已确认的敌人收益不重复发放。未领取完的宝箱房保留；离开NPC房后继续下一房。最终Boss已击败但宝箱未开或奖励未领完时，继续回到本房领取，敌人不重生，冻结候选与已领取事实保留；全部领奖后仍需走到出口确认结算。</x:v>
+        <x:v>暂离主城保留关卡背包、角色收益和消耗。未完成的怪物或Boss战再次进入时重开，已确认的敌人收益不重复发放。未领取完的宝箱房保留；离开NPC房后继续下一房。最终Boss已击败但宝箱未开或尚未领取时，继续回到本房领取，敌人不重生，整箱冻结物品保持不变；一键领取全部后仍需走到出口确认结算。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
